--- a/healthcare_surveys/023_health_informatics_system_usability_evaluation_form--healthcare_surveys.xlsx
+++ b/healthcare_surveys/023_health_informatics_system_usability_evaluation_form--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -712,12 +712,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>navigation_menu</t>
+          <t>navigation_menu_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>navigation menu</t>
+          <t>Navigation Menu 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -735,12 +735,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>search_bar</t>
+          <t>search_bar_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>search bar</t>
+          <t>Search Bar 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -758,12 +758,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>search_bar_visibility</t>
+          <t>search_bar_visibility_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>search bar visibility</t>
+          <t>Search Bar Visibility 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -781,12 +781,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>navigation_speed</t>
+          <t>navigation_speed_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>navigation speed</t>
+          <t>Navigation Speed 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -950,12 +950,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>user_interface</t>
+          <t>user_interface_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>user interface</t>
+          <t>User Interface 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>user_interface_speed_rating</t>
+          <t>user_interface_speed_rating_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>user interface speed rating</t>
+          <t>User Interface Speed Rating 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>feedback_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Feedback 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1125,9 +1125,9 @@
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'not_clear_or_hard_to_use',_'value':_1}</t>
+          <t>not_clear_or_hard_to_use</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Not clear or hard to use', 'value': 1}</t>
+          <t>Not clear or hard to use</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_clear_but_hard_to_navigate',_'value':_2}</t>
+          <t>somewhat_clear_but_hard_to_navigate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat clear but hard to navigate', 'value': 2}</t>
+          <t>Somewhat clear but hard to navigate</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'easy_to_use',_'value':_3}</t>
+          <t>easy_to_use</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Easy to use', 'value': 3}</t>
+          <t>Easy to use</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'very_easy_to_use',_'value':_4}</t>
+          <t>very_easy_to_use</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Very easy to use', 'value': 4}</t>
+          <t>Very easy to use</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_easy_to_use',_'value':_5}</t>
+          <t>extremely_easy_to_use</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely easy to use', 'value': 5}</t>
+          <t>Extremely easy to use</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'always_visible',_'value':_1}</t>
+          <t>always_visible</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Always visible', 'value': 1}</t>
+          <t>Always visible</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes_visible',_'value':_2}</t>
+          <t>sometimes_visible</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes visible', 'value': 2}</t>
+          <t>Sometimes visible</t>
         </is>
       </c>
     </row>
@@ -1274,148 +1274,148 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'never_visible',_'value':_3}</t>
+          <t>never_visible</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Never visible', 'value': 3}</t>
+          <t>Never visible</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>navigation_menu_choices</t>
+          <t>navigation_menu_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not_clear_or_hard_to_use',_'value':_1}</t>
+          <t>not_clear_or_hard_to_use</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Not clear or hard to use', 'value': 1}</t>
+          <t>Not clear or hard to use</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>navigation_menu_choices</t>
+          <t>navigation_menu_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_clear_but_hard_to_navigate',_'value':_2}</t>
+          <t>somewhat_clear_but_hard_to_navigate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat clear but hard to navigate', 'value': 2}</t>
+          <t>Somewhat clear but hard to navigate</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>navigation_menu_choices</t>
+          <t>navigation_menu_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'easy_to_use',_'value':_3}</t>
+          <t>easy_to_use</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Easy to use', 'value': 3}</t>
+          <t>Easy to use</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>navigation_menu_choices</t>
+          <t>navigation_menu_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'very_easy_to_use',_'value':_4}</t>
+          <t>very_easy_to_use</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Very easy to use', 'value': 4}</t>
+          <t>Very easy to use</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>navigation_menu_choices</t>
+          <t>navigation_menu_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_easy_to_use',_'value':_5}</t>
+          <t>extremely_easy_to_use</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely easy to use', 'value': 5}</t>
+          <t>Extremely easy to use</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>search_bar_visibility_choices</t>
+          <t>search_bar_visibility_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'always_visible',_'value':_1}</t>
+          <t>always_visible</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Always visible', 'value': 1}</t>
+          <t>Always visible</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>search_bar_visibility_choices</t>
+          <t>search_bar_visibility_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes_visible',_'value':_2}</t>
+          <t>sometimes_visible</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes visible', 'value': 2}</t>
+          <t>Sometimes visible</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>search_bar_visibility_choices</t>
+          <t>search_bar_visibility_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'never_visible',_'value':_3}</t>
+          <t>never_visible</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Never visible', 'value': 3}</t>
+          <t>Never visible</t>
         </is>
       </c>
     </row>
